--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$8</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="100">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:42:19+00:00</t>
+    <t>2026-07-09T18:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L'archive de Portabilité est un conteneur structuré, regroupant l'ensemble des documents et données LGC exportées ainsi que les éléments de métadonnées, d'index et de documentation nécessaires à leur exploitation par le destinataire.</t>
+    <t>L'archive de Portabilité est un conteneur structuré, regroupant l'ensemble des documents et données LGC exportées ainsi que les éléments de métadonnées, d'index et de documentation nécessaires à leur exploitation par le destinataire. Convention de nommage : PAAAAAMMJJThhmmss.ZIP, avec PA = préfixe, AAAAMMJJThhmmss = horodatage</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -250,13 +250,16 @@
 </t>
   </si>
   <si>
+    <t>L'archive de Portabilité est un conteneur structuré, regroupant l'ensemble des documents et données LGC exportées ainsi que les éléments de métadonnées, d'index et de documentation nécessaires à leur exploitation par le destinataire.</t>
+  </si>
+  <si>
     <t>Transaction ExportArchivePortabilite</t>
   </si>
   <si>
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.INDEX</t>
+    <t>pdlgc-archive-portabilite.README</t>
   </si>
   <si>
     <t>1</t>
@@ -265,11 +268,11 @@
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-index
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-readme
 </t>
   </si>
   <si>
-    <t>Navigation globale</t>
+    <t>Informations éditoriales et instructions d'exploitation de l'archive</t>
   </si>
   <si>
     <t>pdlgc-archive-portabilite.MANIFEST</t>
@@ -282,24 +285,44 @@
     <t>Rapport de volumétrie et d'intégrité</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.TRANSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-repo-transverse
+    <t>pdlgc-archive-portabilite.SIGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-signature
 </t>
   </si>
   <si>
+    <t>signature XAdES de l'archive attestant de l'imputabilité et l'intégrité des données</t>
+  </si>
+  <si>
+    <t>pdlgc-archive-portabilite.DOCUMENTATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-documentation
+</t>
+  </si>
+  <si>
+    <t>répertoire de stockage de la documentation d'export (dictionnaire de données, mapping, schémas techniques, jeu d'échantillons,...)</t>
+  </si>
+  <si>
+    <t>pdlgc-archive-portabilite.TRANSVERSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-archive-transverse
+</t>
+  </si>
+  <si>
     <t>Archive de données transverses liées au praticien ou au cabinet (agenda, données de comptabilité, logs d'accès,...)</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.PATXXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-repo-patient
+    <t>pdlgc-archive-portabilite.PATNNNNN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-archive-patient
 </t>
   </si>
   <si>
-    <t>Archive de données médicales liées au patient. Chaque patient est représenté par une archive distincte</t>
+    <t>Archive de données médicales liées au patient, ou NNNNN est incrémenté à partir de 00001. Chaque patient est représenté par une archive distincte conforme au profil IHE_XDM</t>
   </si>
 </sst>
 </file>
@@ -616,11 +639,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="28.62890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.62890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.79296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -629,7 +652,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.62890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -650,7 +673,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.62890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -797,13 +820,13 @@
         <v>76</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -853,7 +876,7 @@
         <v>73</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>74</v>
@@ -870,10 +893,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -881,13 +904,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>73</v>
@@ -896,13 +919,13 @@
         <v>73</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -953,13 +976,13 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -970,10 +993,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -981,13 +1004,13 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>73</v>
@@ -996,13 +1019,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1053,13 +1076,13 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
@@ -1070,10 +1093,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1081,13 +1104,13 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>73</v>
@@ -1096,13 +1119,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1153,13 +1176,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1170,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1181,13 +1204,13 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>73</v>
@@ -1196,13 +1219,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1253,23 +1276,223 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
+      <c r="H8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6">
+  <autoFilter ref="A1:AJ8">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -1279,7 +1502,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI5">
+  <conditionalFormatting sqref="A2:AI7">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,7 +272,7 @@
 </t>
   </si>
   <si>
-    <t>Informations éditoriales et instructions d'exploitation de l'archive</t>
+    <t>Informations éditoriales et instructions d'exploitation de l'archive de portabilité.</t>
   </si>
   <si>
     <t>pdlgc-archive-portabilite.MANIFEST</t>
@@ -282,7 +282,7 @@
 </t>
   </si>
   <si>
-    <t>Rapport de volumétrie et d'intégrité</t>
+    <t>Vue synthétique du contenu de l'archive de portabilité, incluant rapport de volumétrie et d'intégrité.</t>
   </si>
   <si>
     <t>pdlgc-archive-portabilite.SIGN</t>
@@ -292,7 +292,7 @@
 </t>
   </si>
   <si>
-    <t>signature XAdES de l'archive attestant de l'imputabilité et l'intégrité des données</t>
+    <t>signature XAdES de l'archive attestant de l'imputabilité et l'intégrité des données.</t>
   </si>
   <si>
     <t>pdlgc-archive-portabilite.DOCUMENTATION</t>
@@ -302,7 +302,7 @@
 </t>
   </si>
   <si>
-    <t>répertoire de stockage de la documentation d'export (dictionnaire de données, mapping, schémas techniques, jeu d'échantillons,...)</t>
+    <t>répertoire de stockage de la documentation d'export permettant l'interprétation de l'archive par le système destinataire (dictionnaire de données, mapping, schémas techniques, jeu d'échantillons,...).</t>
   </si>
   <si>
     <t>pdlgc-archive-portabilite.TRANSVERSE</t>
@@ -312,7 +312,7 @@
 </t>
   </si>
   <si>
-    <t>Archive de données transverses liées au praticien ou au cabinet (agenda, données de comptabilité, logs d'accès,...)</t>
+    <t>Archive de données transverses liées au praticien ou au cabinet (agenda, données de comptabilité, logs d'accès,...).</t>
   </si>
   <si>
     <t>pdlgc-archive-portabilite.PATNNNNN</t>
@@ -322,7 +322,7 @@
 </t>
   </si>
   <si>
-    <t>Archive de données médicales liées au patient, ou NNNNN est incrémenté à partir de 00001. Chaque patient est représenté par une archive distincte conforme au profil IHE_XDM</t>
+    <t>Archive de données médicales liées au patient, ou NNNNN est incrémenté à partir de 00001. Chaque patient est représenté par une archive distincte conforme au profil IHE_XDM.</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>81</v>
@@ -1379,7 +1379,7 @@
         <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>81</v>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -259,7 +259,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.README</t>
+    <t>pdlgc-archive-portabilite.readme</t>
   </si>
   <si>
     <t>1</t>
@@ -275,7 +275,7 @@
     <t>Informations éditoriales et instructions d'exploitation de l'archive de portabilité.</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.MANIFEST</t>
+    <t>pdlgc-archive-portabilite.manifest</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-manifest
@@ -285,7 +285,7 @@
     <t>Vue synthétique du contenu de l'archive de portabilité, incluant rapport de volumétrie et d'intégrité.</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.SIGN</t>
+    <t>pdlgc-archive-portabilite.signature</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-signature
@@ -295,7 +295,7 @@
     <t>signature XAdES de l'archive attestant de l'imputabilité et l'intégrité des données.</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.DOCUMENTATION</t>
+    <t>pdlgc-archive-portabilite.Documentation</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-documentation
@@ -305,7 +305,7 @@
     <t>répertoire de stockage de la documentation d'export permettant l'interprétation de l'archive par le système destinataire (dictionnaire de données, mapping, schémas techniques, jeu d'échantillons,...).</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.TRANSVERSE</t>
+    <t>pdlgc-archive-portabilite.ArchiveTransverse</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-archive-transverse
@@ -315,14 +315,14 @@
     <t>Archive de données transverses liées au praticien ou au cabinet (agenda, données de comptabilité, logs d'accès,...).</t>
   </si>
   <si>
-    <t>pdlgc-archive-portabilite.PATNNNNN</t>
+    <t>pdlgc-archive-portabilite.ArchivePatient</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-archive-patient
 </t>
   </si>
   <si>
-    <t>Archive de données médicales liées au patient, ou NNNNN est incrémenté à partir de 00001. Chaque patient est représenté par une archive distincte conforme au profil IHE_XDM.</t>
+    <t>Archive de données médicales liées au patient respectant le nommage `PATNNNNN` ou NNNNN est incrémenté à partir de 00001. Chaque patient est représenté par une archive distincte conforme au profil IHE_XDM.</t>
   </si>
 </sst>
 </file>
@@ -642,8 +642,8 @@
   <dimension ref="A1:AJ8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.79296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.33203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.33203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -673,7 +673,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.33203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-portabilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
